--- a/data/trans_camb/IP1001-Dificultad-trans_camb.xlsx
+++ b/data/trans_camb/IP1001-Dificultad-trans_camb.xlsx
@@ -40,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -66,13 +66,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -513,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -524,9 +517,6 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -542,68 +532,50 @@
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Niña</t>
         </is>
       </c>
-      <c r="G1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2012/2007</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2016/2007</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2023/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
     </row>
@@ -616,9 +588,6 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -631,15 +600,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr"/>
-      <c r="D4" s="5" t="inlineStr"/>
-      <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="5" t="inlineStr"/>
-      <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr"/>
-      <c r="J4" s="5" t="inlineStr"/>
-      <c r="K4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="n">
+        <v>-0.3938319229502125</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.7632149084558393</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>1.333181930544088</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>1.961298650038313</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>0.4359860312213963</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>1.337161019009295</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
@@ -648,15 +626,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr"/>
-      <c r="D5" s="5" t="inlineStr"/>
-      <c r="E5" s="5" t="inlineStr"/>
-      <c r="F5" s="5" t="inlineStr"/>
-      <c r="G5" s="5" t="inlineStr"/>
-      <c r="H5" s="5" t="inlineStr"/>
-      <c r="I5" s="5" t="inlineStr"/>
-      <c r="J5" s="5" t="inlineStr"/>
-      <c r="K5" s="5" t="inlineStr"/>
+      <c r="C5" s="5" t="n">
+        <v>-2.571977630092988</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-1.871247336726273</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-0.8239460397076882</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-1.033132022990996</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>-1.17031281490825</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>-0.9577693474869694</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
@@ -665,15 +652,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
-      <c r="J6" s="5" t="inlineStr"/>
-      <c r="K6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="n">
+        <v>1.648104126744344</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>4.996619602798359</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>3.538518386520756</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>7.63988261539469</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>2.128586696345447</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>4.43221308765542</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
@@ -682,15 +678,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr"/>
-      <c r="D7" s="6" t="inlineStr"/>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="6" t="inlineStr"/>
-      <c r="H7" s="6" t="inlineStr"/>
-      <c r="I7" s="6" t="inlineStr"/>
-      <c r="J7" s="6" t="inlineStr"/>
-      <c r="K7" s="6" t="inlineStr"/>
+      <c r="C7" s="6" t="n">
+        <v>-0.1577476895139882</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>0.3057024618767605</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>0.7453885378907967</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>1.096571667846278</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.2026392834780343</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.6214908996687695</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
@@ -699,15 +704,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr"/>
-      <c r="D8" s="6" t="inlineStr"/>
-      <c r="E8" s="6" t="inlineStr"/>
-      <c r="F8" s="6" t="inlineStr"/>
-      <c r="G8" s="6" t="inlineStr"/>
-      <c r="H8" s="6" t="inlineStr"/>
-      <c r="I8" s="6" t="inlineStr"/>
-      <c r="J8" s="6" t="inlineStr"/>
-      <c r="K8" s="6" t="inlineStr"/>
+      <c r="C8" s="6" t="n">
+        <v>-0.6807899672250661</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>-0.6281413736066408</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>-0.3787272662657754</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>-0.6498997562918138</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.3988168475714259</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.4255675548174926</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
@@ -716,15 +730,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr"/>
-      <c r="D9" s="6" t="inlineStr"/>
-      <c r="E9" s="6" t="inlineStr"/>
-      <c r="F9" s="6" t="inlineStr"/>
-      <c r="G9" s="6" t="inlineStr"/>
-      <c r="H9" s="6" t="inlineStr"/>
-      <c r="I9" s="6" t="inlineStr"/>
-      <c r="J9" s="6" t="inlineStr"/>
-      <c r="K9" s="6" t="inlineStr"/>
+      <c r="C9" s="6" t="n">
+        <v>1.422137506690595</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>3.342467248909118</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>4.481693054620695</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>9.970587585511508</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>1.471036159034416</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>2.635435481669325</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -737,15 +760,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="inlineStr"/>
-      <c r="F10" s="5" t="inlineStr"/>
-      <c r="G10" s="5" t="inlineStr"/>
-      <c r="H10" s="5" t="inlineStr"/>
-      <c r="I10" s="5" t="inlineStr"/>
-      <c r="J10" s="5" t="inlineStr"/>
-      <c r="K10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="n">
+        <v>0.4551385605381347</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.1131000364092517</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-0.5995732925592208</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-0.1655183929172528</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>-0.06987144336002456</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>-0.007238341666465295</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
@@ -754,15 +786,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr"/>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="inlineStr"/>
-      <c r="F11" s="5" t="inlineStr"/>
-      <c r="G11" s="5" t="inlineStr"/>
-      <c r="H11" s="5" t="inlineStr"/>
-      <c r="I11" s="5" t="inlineStr"/>
-      <c r="J11" s="5" t="inlineStr"/>
-      <c r="K11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="n">
+        <v>-2.318407878055321</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-2.406266670658567</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-2.804785377379554</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-2.51342060352835</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>-1.921734818326839</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>-1.615583083008856</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
@@ -771,15 +812,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr"/>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="inlineStr"/>
-      <c r="F12" s="5" t="inlineStr"/>
-      <c r="G12" s="5" t="inlineStr"/>
-      <c r="H12" s="5" t="inlineStr"/>
-      <c r="I12" s="5" t="inlineStr"/>
-      <c r="J12" s="5" t="inlineStr"/>
-      <c r="K12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="n">
+        <v>2.822060886879924</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>2.912007110534776</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>1.372673799646491</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>2.228519070612795</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>1.555818434626955</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>1.919976236962528</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
@@ -788,15 +838,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr"/>
-      <c r="D13" s="6" t="inlineStr"/>
-      <c r="E13" s="6" t="inlineStr"/>
-      <c r="F13" s="6" t="inlineStr"/>
-      <c r="G13" s="6" t="inlineStr"/>
-      <c r="H13" s="6" t="inlineStr"/>
-      <c r="I13" s="6" t="inlineStr"/>
-      <c r="J13" s="6" t="inlineStr"/>
-      <c r="K13" s="6" t="inlineStr"/>
+      <c r="C13" s="6" t="n">
+        <v>0.1766827760463527</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>0.04390493387355134</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>-0.2723040462158107</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>-0.07517234118638559</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.02925178023225165</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.003030342146825212</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
@@ -805,15 +864,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr"/>
-      <c r="D14" s="6" t="inlineStr"/>
-      <c r="E14" s="6" t="inlineStr"/>
-      <c r="F14" s="6" t="inlineStr"/>
-      <c r="G14" s="6" t="inlineStr"/>
-      <c r="H14" s="6" t="inlineStr"/>
-      <c r="I14" s="6" t="inlineStr"/>
-      <c r="J14" s="6" t="inlineStr"/>
-      <c r="K14" s="6" t="inlineStr"/>
+      <c r="C14" s="6" t="n">
+        <v>-0.5929055300354188</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>-0.6541728551918006</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>-0.8782442690106601</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-0.8378728886608994</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.5747466599106215</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.5286630503744835</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
@@ -822,15 +890,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr"/>
-      <c r="D15" s="6" t="inlineStr"/>
-      <c r="E15" s="6" t="inlineStr"/>
-      <c r="F15" s="6" t="inlineStr"/>
-      <c r="G15" s="6" t="inlineStr"/>
-      <c r="H15" s="6" t="inlineStr"/>
-      <c r="I15" s="6" t="inlineStr"/>
-      <c r="J15" s="6" t="inlineStr"/>
-      <c r="K15" s="6" t="inlineStr"/>
+      <c r="C15" s="6" t="n">
+        <v>1.888409388438318</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>2.067951549774886</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>1.494015907266173</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>1.965619893443414</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>1.055390876442989</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>1.305004800309559</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -843,15 +920,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr"/>
-      <c r="D16" s="5" t="inlineStr"/>
-      <c r="E16" s="5" t="inlineStr"/>
-      <c r="F16" s="5" t="inlineStr"/>
-      <c r="G16" s="5" t="inlineStr"/>
-      <c r="H16" s="5" t="inlineStr"/>
-      <c r="I16" s="5" t="inlineStr"/>
-      <c r="J16" s="5" t="inlineStr"/>
-      <c r="K16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="n">
+        <v>0.3318186191380596</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>1.427988192081404</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.9142225244951859</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>1.215930499379134</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>0.5924932278352227</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>1.407137542636187</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
@@ -860,15 +946,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr"/>
-      <c r="D17" s="5" t="inlineStr"/>
-      <c r="E17" s="5" t="inlineStr"/>
-      <c r="F17" s="5" t="inlineStr"/>
-      <c r="G17" s="5" t="inlineStr"/>
-      <c r="H17" s="5" t="inlineStr"/>
-      <c r="I17" s="5" t="inlineStr"/>
-      <c r="J17" s="5" t="inlineStr"/>
-      <c r="K17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="n">
+        <v>-2.921831069953722</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-1.950714099351717</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-1.323380104737376</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-1.185092430452523</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>-1.403983794567783</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>-0.8032191852019813</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
@@ -877,15 +972,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr"/>
-      <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="5" t="inlineStr"/>
-      <c r="F18" s="5" t="inlineStr"/>
-      <c r="G18" s="5" t="inlineStr"/>
-      <c r="H18" s="5" t="inlineStr"/>
-      <c r="I18" s="5" t="inlineStr"/>
-      <c r="J18" s="5" t="inlineStr"/>
-      <c r="K18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="n">
+        <v>4.054594724634054</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>4.638446744273178</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>3.759751683279971</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>3.591978409951552</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>2.691596227623141</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>3.59675472882394</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
@@ -894,15 +998,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr"/>
-      <c r="D19" s="6" t="inlineStr"/>
-      <c r="E19" s="6" t="inlineStr"/>
-      <c r="F19" s="6" t="inlineStr"/>
-      <c r="G19" s="6" t="inlineStr"/>
-      <c r="H19" s="6" t="inlineStr"/>
-      <c r="I19" s="6" t="inlineStr"/>
-      <c r="J19" s="6" t="inlineStr"/>
-      <c r="K19" s="6" t="inlineStr"/>
+      <c r="C19" s="6" t="n">
+        <v>0.1120971421014262</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>0.4824123363020391</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>0.8319215490855055</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>1.106468892989004</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>0.289495866285371</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>0.6875361316389956</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n"/>
@@ -911,15 +1024,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr"/>
-      <c r="D20" s="6" t="inlineStr"/>
-      <c r="E20" s="6" t="inlineStr"/>
-      <c r="F20" s="6" t="inlineStr"/>
-      <c r="G20" s="6" t="inlineStr"/>
-      <c r="H20" s="6" t="inlineStr"/>
-      <c r="I20" s="6" t="inlineStr"/>
-      <c r="J20" s="6" t="inlineStr"/>
-      <c r="K20" s="6" t="inlineStr"/>
+      <c r="C20" s="6" t="n">
+        <v>-0.7264021708605797</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>-0.508664761145423</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>-0.8076454145746417</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>-0.499919285053037</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>-0.3129677744799941</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
@@ -928,15 +1050,20 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr"/>
-      <c r="D21" s="6" t="inlineStr"/>
+      <c r="C21" s="6" t="n">
+        <v>2.837164578055987</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>3.66088066095532</v>
+      </c>
       <c r="E21" s="6" t="inlineStr"/>
       <c r="F21" s="6" t="inlineStr"/>
-      <c r="G21" s="6" t="inlineStr"/>
-      <c r="H21" s="6" t="inlineStr"/>
-      <c r="I21" s="6" t="inlineStr"/>
-      <c r="J21" s="6" t="inlineStr"/>
-      <c r="K21" s="6" t="inlineStr"/>
+      <c r="G21" s="6" t="n">
+        <v>2.516239018553772</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>3.274543722391492</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -949,15 +1076,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr"/>
-      <c r="D22" s="5" t="inlineStr"/>
-      <c r="E22" s="5" t="inlineStr"/>
-      <c r="F22" s="5" t="inlineStr"/>
-      <c r="G22" s="5" t="inlineStr"/>
-      <c r="H22" s="5" t="inlineStr"/>
-      <c r="I22" s="5" t="inlineStr"/>
-      <c r="J22" s="5" t="inlineStr"/>
-      <c r="K22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="n">
+        <v>-0.6434206097650232</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>0.2787336829355912</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>-1.637306599268501</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>-0.2874035138117397</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>-1.075615019310628</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>-0.01311251396517964</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n"/>
@@ -966,15 +1102,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr"/>
-      <c r="D23" s="5" t="inlineStr"/>
-      <c r="E23" s="5" t="inlineStr"/>
-      <c r="F23" s="5" t="inlineStr"/>
-      <c r="G23" s="5" t="inlineStr"/>
-      <c r="H23" s="5" t="inlineStr"/>
-      <c r="I23" s="5" t="inlineStr"/>
-      <c r="J23" s="5" t="inlineStr"/>
-      <c r="K23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="n">
+        <v>-4.332287636436551</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-3.76593358375397</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-5.83520093252625</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-4.525971121918542</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>-4.101987919610772</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>-2.642442163710502</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n"/>
@@ -983,15 +1128,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr"/>
-      <c r="D24" s="5" t="inlineStr"/>
-      <c r="E24" s="5" t="inlineStr"/>
-      <c r="F24" s="5" t="inlineStr"/>
-      <c r="G24" s="5" t="inlineStr"/>
-      <c r="H24" s="5" t="inlineStr"/>
-      <c r="I24" s="5" t="inlineStr"/>
-      <c r="J24" s="5" t="inlineStr"/>
-      <c r="K24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="n">
+        <v>2.957564761626076</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>4.160596234330543</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>1.196736855622873</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>2.705059078978168</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>1.208274584137551</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>2.666590698866415</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n"/>
@@ -1000,15 +1154,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr"/>
-      <c r="D25" s="6" t="inlineStr"/>
-      <c r="E25" s="6" t="inlineStr"/>
-      <c r="F25" s="6" t="inlineStr"/>
-      <c r="G25" s="6" t="inlineStr"/>
-      <c r="H25" s="6" t="inlineStr"/>
-      <c r="I25" s="6" t="inlineStr"/>
-      <c r="J25" s="6" t="inlineStr"/>
-      <c r="K25" s="6" t="inlineStr"/>
+      <c r="C25" s="6" t="n">
+        <v>-0.2266049303121115</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>0.09816662046359487</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>-0.651235580230245</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>-0.1143142000166739</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>-0.3994508855145332</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>-0.004869591090378831</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n"/>
@@ -1017,15 +1180,20 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr"/>
+      <c r="C26" s="6" t="n">
+        <v>-1</v>
+      </c>
       <c r="D26" s="6" t="inlineStr"/>
       <c r="E26" s="6" t="inlineStr"/>
-      <c r="F26" s="6" t="inlineStr"/>
-      <c r="G26" s="6" t="inlineStr"/>
-      <c r="H26" s="6" t="inlineStr"/>
-      <c r="I26" s="6" t="inlineStr"/>
-      <c r="J26" s="6" t="inlineStr"/>
-      <c r="K26" s="6" t="inlineStr"/>
+      <c r="F26" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>-0.8863878173163842</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>-0.6510610198108632</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n"/>
@@ -1034,15 +1202,20 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr"/>
+      <c r="C27" s="6" t="n">
+        <v>4.924020883306601</v>
+      </c>
       <c r="D27" s="6" t="inlineStr"/>
       <c r="E27" s="6" t="inlineStr"/>
-      <c r="F27" s="6" t="inlineStr"/>
-      <c r="G27" s="6" t="inlineStr"/>
-      <c r="H27" s="6" t="inlineStr"/>
-      <c r="I27" s="6" t="inlineStr"/>
-      <c r="J27" s="6" t="inlineStr"/>
-      <c r="K27" s="6" t="inlineStr"/>
+      <c r="F27" s="6" t="n">
+        <v>5.427150433765896</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>1.378612474422962</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>2.888275854111104</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -1055,15 +1228,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr"/>
-      <c r="D28" s="5" t="inlineStr"/>
-      <c r="E28" s="5" t="inlineStr"/>
-      <c r="F28" s="5" t="inlineStr"/>
-      <c r="G28" s="5" t="inlineStr"/>
-      <c r="H28" s="5" t="inlineStr"/>
-      <c r="I28" s="5" t="inlineStr"/>
-      <c r="J28" s="5" t="inlineStr"/>
-      <c r="K28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="n">
+        <v>-0.06089496543496241</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>0.7678203762286697</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>0.3320882741191178</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>0.5604773216862303</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>0.132029717749067</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>0.6862855539014932</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n"/>
@@ -1072,15 +1254,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr"/>
-      <c r="D29" s="5" t="inlineStr"/>
-      <c r="E29" s="5" t="inlineStr"/>
-      <c r="F29" s="5" t="inlineStr"/>
-      <c r="G29" s="5" t="inlineStr"/>
-      <c r="H29" s="5" t="inlineStr"/>
-      <c r="I29" s="5" t="inlineStr"/>
-      <c r="J29" s="5" t="inlineStr"/>
-      <c r="K29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="n">
+        <v>-1.577494483863582</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>-1.007551296596578</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>-0.9887932687744464</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>-0.8276040322882231</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>-0.8879134661604617</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>-0.3628050751645301</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n"/>
@@ -1089,15 +1280,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr"/>
-      <c r="D30" s="5" t="inlineStr"/>
-      <c r="E30" s="5" t="inlineStr"/>
-      <c r="F30" s="5" t="inlineStr"/>
-      <c r="G30" s="5" t="inlineStr"/>
-      <c r="H30" s="5" t="inlineStr"/>
-      <c r="I30" s="5" t="inlineStr"/>
-      <c r="J30" s="5" t="inlineStr"/>
-      <c r="K30" s="5" t="inlineStr"/>
+      <c r="C30" s="5" t="n">
+        <v>1.244936829051304</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>2.323269025252072</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>1.542969486358815</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>2.072334401624027</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>1.045942253159711</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>1.696605239271326</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n"/>
@@ -1106,15 +1306,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr"/>
-      <c r="D31" s="6" t="inlineStr"/>
-      <c r="E31" s="6" t="inlineStr"/>
-      <c r="F31" s="6" t="inlineStr"/>
-      <c r="G31" s="6" t="inlineStr"/>
-      <c r="H31" s="6" t="inlineStr"/>
-      <c r="I31" s="6" t="inlineStr"/>
-      <c r="J31" s="6" t="inlineStr"/>
-      <c r="K31" s="6" t="inlineStr"/>
+      <c r="C31" s="6" t="n">
+        <v>-0.02282753158025745</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>0.287830755155694</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>0.1794228215193986</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>0.3028183476857962</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>0.05818218098141794</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>0.3024288090800793</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n"/>
@@ -1123,15 +1332,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr"/>
-      <c r="D32" s="6" t="inlineStr"/>
-      <c r="E32" s="6" t="inlineStr"/>
-      <c r="F32" s="6" t="inlineStr"/>
-      <c r="G32" s="6" t="inlineStr"/>
-      <c r="H32" s="6" t="inlineStr"/>
-      <c r="I32" s="6" t="inlineStr"/>
-      <c r="J32" s="6" t="inlineStr"/>
-      <c r="K32" s="6" t="inlineStr"/>
+      <c r="C32" s="6" t="n">
+        <v>-0.4644737838645344</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>-0.2920050056865737</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>-0.4029705849971311</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>-0.3420747313768264</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>-0.3206434171816149</v>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>-0.1562673297294619</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n"/>
@@ -1140,15 +1358,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr"/>
-      <c r="D33" s="6" t="inlineStr"/>
-      <c r="E33" s="6" t="inlineStr"/>
-      <c r="F33" s="6" t="inlineStr"/>
-      <c r="G33" s="6" t="inlineStr"/>
-      <c r="H33" s="6" t="inlineStr"/>
-      <c r="I33" s="6" t="inlineStr"/>
-      <c r="J33" s="6" t="inlineStr"/>
-      <c r="K33" s="6" t="inlineStr"/>
+      <c r="C33" s="6" t="n">
+        <v>0.6300118684352513</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>1.152046870678966</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>1.210692880951779</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>1.595677380110111</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>0.5719775519634119</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>0.9111396033274303</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1159,11 +1386,11 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A22:A27"/>
     <mergeCell ref="A4:A9"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E1:F1"/>
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A10:A15"/>
     <mergeCell ref="A28:A33"/>
